--- a/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9CF88F-6831-472F-B71E-44D197FEFB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04B5E4B-9527-4590-B824-DE345E9AB11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>9999</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -665,7 +665,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -673,16 +673,9 @@
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1060,177 +1053,177 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="V2" t="s">
+        <v>59</v>
+      </c>
+      <c r="W2" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X2" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Y2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z2" t="s">
         <v>40</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AA2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC2" t="s">
         <v>55</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="AD2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="s">
         <v>61</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1245,13 +1238,13 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1268,18 +1261,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1298,25 +1291,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" t="s">
         <v>77</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1340,54 +1333,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1408,19 +1401,19 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="5"/>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="4"/>
     </row>
@@ -1440,17 +1433,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04B5E4B-9527-4590-B824-DE345E9AB11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BDBC64-4C62-48CF-8356-5BE821133576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -258,12 +258,6 @@
     <t>System Admin</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
     <t>Indrajeet Singh</t>
   </si>
   <si>
@@ -277,6 +271,12 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>Derek Janisch</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1139,7 @@
         <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1160,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s">
         <v>58</v>
@@ -1172,13 +1172,13 @@
         <v>61</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R2" t="s">
         <v>25</v>
@@ -1187,7 +1187,7 @@
         <v>25</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U2" t="s">
         <v>28</v>
@@ -1208,7 +1208,7 @@
         <v>40</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AB2" s="7" t="s">
         <v>62</v>
@@ -1303,13 +1303,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BDBC64-4C62-48CF-8356-5BE821133576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E26F54-4A34-4B7E-A9DB-217E04A653D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
   <si>
     <t>Client</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>Derek Janisch</t>
+  </si>
+  <si>
+    <t>Andy Chen</t>
   </si>
 </sst>
 </file>
@@ -999,38 +1002,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>77</v>
@@ -1235,14 +1238,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A623B104-31C6-42A8-AE98-57FDC2862A9F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1255,22 +1258,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E1B0EF-A5E2-4F8E-85E1-C720437C78C1}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1283,14 +1286,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1301,7 +1304,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -1321,17 +1324,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1357,7 +1360,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1392,26 +1395,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="5"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1426,22 +1429,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9566F5-BF1D-4424-961C-A03D3831C98B}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>68</v>
       </c>

--- a/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E26F54-4A34-4B7E-A9DB-217E04A653D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999C1CB8-DB3E-41EE-9783-234865D89FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>9999</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Eric Winthrop</t>
   </si>
   <si>
@@ -280,6 +274,12 @@
   </si>
   <si>
     <t>Andy Chen</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -1044,189 +1044,189 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF2" t="s">
         <v>60</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="R2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1242,12 +1242,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1265,17 +1265,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1295,24 +1295,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1336,54 +1336,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1404,19 +1404,19 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5"/>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="4"/>
     </row>
@@ -1436,17 +1436,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999C1CB8-DB3E-41EE-9783-234865D89FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004AB617-14CE-48CC-B30E-63C82BD0754E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -1002,38 +1002,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1238,14 +1238,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A623B104-31C6-42A8-AE98-57FDC2862A9F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1258,22 +1258,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E1B0EF-A5E2-4F8E-85E1-C720437C78C1}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1286,14 +1286,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -1324,17 +1324,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1395,26 +1395,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="5"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1429,22 +1429,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9566F5-BF1D-4424-961C-A03D3831C98B}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>

--- a/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
+++ b/TestData/LV_TMTI0054683_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnFROpportunityAndEngagementPage.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6611F104-A45E-40FB-82EE-D9EBB54486BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE8E966-36C6-4BF8-9201-7CD163A5E0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
     <sheet name="AppName" sheetId="6" r:id="rId2"/>
-    <sheet name="ModuleName" sheetId="7" r:id="rId3"/>
-    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId3"/>
+    <sheet name="ModuleName" sheetId="7" r:id="rId4"/>
     <sheet name="AddContact" sheetId="3" r:id="rId5"/>
     <sheet name="AssociatedOpp" sheetId="4" r:id="rId6"/>
     <sheet name="AssociatedEng" sheetId="5" r:id="rId7"/>
@@ -1000,40 +1000,98 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A623B104-31C6-42A8-AE98-57FDC2862A9F}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1235,106 +1293,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A623B104-31C6-42A8-AE98-57FDC2862A9F}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E1B0EF-A5E2-4F8E-85E1-C720437C78C1}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E1B0EF-A5E2-4F8E-85E1-C720437C78C1}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>58</v>
       </c>
@@ -1395,26 +1395,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="5"/>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -1429,22 +1429,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9566F5-BF1D-4424-961C-A03D3831C98B}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
